--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -548,7 +548,7 @@
     <t>The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -563,7 +563,7 @@
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -667,7 +667,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -684,7 +684,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>Source from which this consent is taken</t>
@@ -797,7 +797,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -834,7 +834,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -932,13 +932,13 @@
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -969,7 +969,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -991,7 +991,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.purpose</t>
@@ -1027,7 +1027,7 @@
     <t>The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1045,7 +1045,7 @@
     <t>If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1099,7 +1099,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1426,7 +1426,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.7890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-access-consent.xlsx
+++ b/fhir/StructureDefinition-ehealth-access-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
